--- a/artfynd/A 18881-2023 artfynd.xlsx
+++ b/artfynd/A 18881-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126412699</v>
       </c>
       <c r="B2" t="n">
-        <v>44805</v>
+        <v>44806</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>126412596</v>
       </c>
       <c r="B3" t="n">
-        <v>44800</v>
+        <v>44801</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>126412705</v>
       </c>
       <c r="B4" t="n">
-        <v>44800</v>
+        <v>44801</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18881-2023 artfynd.xlsx
+++ b/artfynd/A 18881-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126412699</v>
+        <v>126412596</v>
       </c>
       <c r="B2" t="n">
-        <v>44806</v>
+        <v>45044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102021</v>
+        <v>102018</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zygaena viciae</t>
+          <t>Zygaena lonicerae</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Scheven, 1777)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -720,14 +720,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lindhem, Sm</t>
+          <t>Gransmåla, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576174</v>
+        <v>576259</v>
       </c>
       <c r="R2" t="n">
-        <v>6295601</v>
+        <v>6295571</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -796,14 +796,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126412596</v>
+        <v>126412705</v>
       </c>
       <c r="B3" t="n">
-        <v>44801</v>
+        <v>45044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -826,12 +826,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -841,14 +841,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gransmåla, Sm</t>
+          <t>Lindhem, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576259</v>
+        <v>576174</v>
       </c>
       <c r="R3" t="n">
-        <v>6295571</v>
+        <v>6295601</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,37 +917,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126412705</v>
+        <v>126412699</v>
       </c>
       <c r="B4" t="n">
-        <v>44801</v>
+        <v>45049</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102018</v>
+        <v>102021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Zygaena lonicerae</t>
+          <t>Zygaena viciae</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scheven, 1777)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,6 +1035,113 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124466064</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gransmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>576217</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6295538</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Åby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Louise Lindroth</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Louise Lindroth</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18881-2023 artfynd.xlsx
+++ b/artfynd/A 18881-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126412596</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126412705</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1035,6 +1050,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126412699</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1142,8 +1162,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124466064</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>